--- a/ユースケース記述テスト仕様書.xlsx
+++ b/ユースケース記述テスト仕様書.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://oohara.sharepoint.com/sites/a_2/Shared Documents/Javaシステム開発/テキストバージョンアップ対応/設計書/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\s_sakagami\git\gamityansoftware\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="47" documentId="13_ncr:1_{0F77545B-AEE8-4539-AAAA-9876A9ED2292}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6419B806-2766-4A12-9B4F-9EBE0626F7CA}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36954345-DC84-4674-99C2-F916AE21C564}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="730" yWindow="340" windowWidth="15130" windowHeight="8470" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="テスト仕様書" sheetId="5" r:id="rId1"/>
@@ -35,15 +35,12 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="185">
   <si>
     <t>ユースケース記述テスト仕様書</t>
     <rPh sb="6" eb="8">
@@ -2082,6 +2079,9 @@
       <t>コウバン</t>
     </rPh>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>期待値通り</t>
   </si>
 </sst>
 </file>
@@ -3065,7 +3065,9 @@
       <c r="G5" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="H5" s="5"/>
+      <c r="H5" s="5" t="s">
+        <v>184</v>
+      </c>
       <c r="I5" s="5"/>
       <c r="J5" s="7"/>
       <c r="K5" s="5"/>
@@ -3089,7 +3091,9 @@
       <c r="G6" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="H6" s="5"/>
+      <c r="H6" s="5" t="s">
+        <v>184</v>
+      </c>
       <c r="I6" s="5"/>
       <c r="J6" s="7"/>
       <c r="K6" s="5"/>
@@ -3110,7 +3114,9 @@
       <c r="G7" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="H7" s="5"/>
+      <c r="H7" s="5" t="s">
+        <v>184</v>
+      </c>
       <c r="I7" s="5"/>
       <c r="J7" s="7"/>
       <c r="K7" s="5"/>
@@ -3131,7 +3137,9 @@
       <c r="G8" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="H8" s="5"/>
+      <c r="H8" s="5" t="s">
+        <v>184</v>
+      </c>
       <c r="I8" s="5"/>
       <c r="J8" s="7"/>
       <c r="K8" s="5"/>
@@ -3155,7 +3163,9 @@
       <c r="G9" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="H9" s="5"/>
+      <c r="H9" s="5" t="s">
+        <v>184</v>
+      </c>
       <c r="I9" s="5"/>
       <c r="J9" s="7"/>
       <c r="K9" s="5"/>
@@ -3175,7 +3185,9 @@
       <c r="G10" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="H10" s="5"/>
+      <c r="H10" s="5" t="s">
+        <v>184</v>
+      </c>
       <c r="I10" s="5"/>
       <c r="J10" s="7"/>
       <c r="K10" s="5"/>
@@ -3201,7 +3213,9 @@
       <c r="G11" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="H11" s="5"/>
+      <c r="H11" s="5" t="s">
+        <v>184</v>
+      </c>
       <c r="I11" s="5"/>
       <c r="J11" s="7"/>
       <c r="K11" s="5"/>
@@ -5650,15 +5664,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="88cc3c26-756f-41ab-80ed-43e7289fee5b">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="55239288-d498-4dd6-9609-491b39ec8fae" xsi:nil="true"/>
-    <MediaLengthInSeconds xmlns="88cc3c26-756f-41ab-80ed-43e7289fee5b" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5869,15 +5880,45 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="88cc3c26-756f-41ab-80ed-43e7289fee5b">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="55239288-d498-4dd6-9609-491b39ec8fae" xsi:nil="true"/>
+    <MediaLengthInSeconds xmlns="88cc3c26-756f-41ab-80ed-43e7289fee5b" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{24E212E4-ADE4-43F3-9F44-32B431C26D50}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9660893E-02E4-4B08-BC00-3F4A8BDDE437}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="88cc3c26-756f-41ab-80ed-43e7289fee5b"/>
+    <ds:schemaRef ds:uri="55239288-d498-4dd6-9609-491b39ec8fae"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC8775BF-FCD4-4761-95F0-599CE77DEFAA}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
@@ -5890,18 +5931,8 @@
     <ds:schemaRef ds:uri="96e9746f-acab-410f-8363-815e1ac6f97e"/>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9660893E-02E4-4B08-BC00-3F4A8BDDE437}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{24E212E4-ADE4-43F3-9F44-32B431C26D50}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="88cc3c26-756f-41ab-80ed-43e7289fee5b"/>
+    <ds:schemaRef ds:uri="55239288-d498-4dd6-9609-491b39ec8fae"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/ユースケース記述テスト仕様書.xlsx
+++ b/ユースケース記述テスト仕様書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\s_sakagami\git\gamityansoftware\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36954345-DC84-4674-99C2-F916AE21C564}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA3005B2-3271-47BF-943E-0C95FE843877}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="730" yWindow="340" windowWidth="15130" windowHeight="8470" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3510" yWindow="1140" windowWidth="15130" windowHeight="8470" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="テスト仕様書" sheetId="5" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="186">
   <si>
     <t>ユースケース記述テスト仕様書</t>
     <rPh sb="6" eb="8">
@@ -2082,6 +2082,13 @@
   </si>
   <si>
     <t>期待値通り</t>
+  </si>
+  <si>
+    <t>坂上</t>
+    <rPh sb="0" eb="2">
+      <t>サカガミ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
@@ -3118,8 +3125,12 @@
         <v>184</v>
       </c>
       <c r="I7" s="5"/>
-      <c r="J7" s="7"/>
-      <c r="K7" s="5"/>
+      <c r="J7" s="7">
+        <v>46156</v>
+      </c>
+      <c r="K7" s="5" t="s">
+        <v>185</v>
+      </c>
       <c r="L7" s="5"/>
       <c r="M7" s="5"/>
       <c r="P7" s="40"/>
@@ -3141,8 +3152,12 @@
         <v>184</v>
       </c>
       <c r="I8" s="5"/>
-      <c r="J8" s="7"/>
-      <c r="K8" s="5"/>
+      <c r="J8" s="7">
+        <v>46156</v>
+      </c>
+      <c r="K8" s="5" t="s">
+        <v>185</v>
+      </c>
       <c r="L8" s="5"/>
       <c r="M8" s="5"/>
     </row>
@@ -3167,8 +3182,12 @@
         <v>184</v>
       </c>
       <c r="I9" s="5"/>
-      <c r="J9" s="7"/>
-      <c r="K9" s="5"/>
+      <c r="J9" s="7">
+        <v>46156</v>
+      </c>
+      <c r="K9" s="5" t="s">
+        <v>185</v>
+      </c>
       <c r="L9" s="5"/>
       <c r="M9" s="5"/>
     </row>
@@ -3189,8 +3208,12 @@
         <v>184</v>
       </c>
       <c r="I10" s="5"/>
-      <c r="J10" s="7"/>
-      <c r="K10" s="5"/>
+      <c r="J10" s="7">
+        <v>46156</v>
+      </c>
+      <c r="K10" s="5" t="s">
+        <v>185</v>
+      </c>
       <c r="L10" s="5"/>
       <c r="M10" s="5"/>
     </row>
@@ -3217,8 +3240,12 @@
         <v>184</v>
       </c>
       <c r="I11" s="5"/>
-      <c r="J11" s="7"/>
-      <c r="K11" s="5"/>
+      <c r="J11" s="7">
+        <v>46156</v>
+      </c>
+      <c r="K11" s="5" t="s">
+        <v>185</v>
+      </c>
       <c r="L11" s="5"/>
       <c r="M11" s="5"/>
     </row>
@@ -5673,6 +5700,18 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="88cc3c26-756f-41ab-80ed-43e7289fee5b">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="55239288-d498-4dd6-9609-491b39ec8fae" xsi:nil="true"/>
+    <MediaLengthInSeconds xmlns="88cc3c26-756f-41ab-80ed-43e7289fee5b" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x01010058BEBA3CD4E69545839402B5D4E5400B" ma:contentTypeVersion="13" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="85fadafb228503a8e253560e9cdffc69">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="88cc3c26-756f-41ab-80ed-43e7289fee5b" xmlns:ns3="55239288-d498-4dd6-9609-491b39ec8fae" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9785dde68d2e35ac7b66dd15e8e44124" ns2:_="" ns3:_="">
     <xsd:import namespace="88cc3c26-756f-41ab-80ed-43e7289fee5b"/>
@@ -5879,18 +5918,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="88cc3c26-756f-41ab-80ed-43e7289fee5b">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="55239288-d498-4dd6-9609-491b39ec8fae" xsi:nil="true"/>
-    <MediaLengthInSeconds xmlns="88cc3c26-756f-41ab-80ed-43e7289fee5b" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{24E212E4-ADE4-43F3-9F44-32B431C26D50}">
   <ds:schemaRefs>
@@ -5900,6 +5927,25 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC8775BF-FCD4-4761-95F0-599CE77DEFAA}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="4707ffff-3746-4042-a13f-bfbbbbe730e0"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="96e9746f-acab-410f-8363-815e1ac6f97e"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="88cc3c26-756f-41ab-80ed-43e7289fee5b"/>
+    <ds:schemaRef ds:uri="55239288-d498-4dd6-9609-491b39ec8fae"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9660893E-02E4-4B08-BC00-3F4A8BDDE437}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5916,23 +5962,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC8775BF-FCD4-4761-95F0-599CE77DEFAA}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="4707ffff-3746-4042-a13f-bfbbbbe730e0"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="96e9746f-acab-410f-8363-815e1ac6f97e"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="88cc3c26-756f-41ab-80ed-43e7289fee5b"/>
-    <ds:schemaRef ds:uri="55239288-d498-4dd6-9609-491b39ec8fae"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/ユースケース記述テスト仕様書.xlsx
+++ b/ユースケース記述テスト仕様書.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\s_sakagami\git\gamityansoftware\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA3005B2-3271-47BF-943E-0C95FE843877}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40F34AC9-C9D7-436B-B57D-DCDE5260B7AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3510" yWindow="1140" windowWidth="15130" windowHeight="8470" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="186">
   <si>
     <t>ユースケース記述テスト仕様書</t>
     <rPh sb="6" eb="8">
@@ -3076,8 +3076,12 @@
         <v>184</v>
       </c>
       <c r="I5" s="5"/>
-      <c r="J5" s="7"/>
-      <c r="K5" s="5"/>
+      <c r="J5" s="7">
+        <v>46156</v>
+      </c>
+      <c r="K5" s="5" t="s">
+        <v>185</v>
+      </c>
       <c r="L5" s="5"/>
       <c r="M5" s="5"/>
     </row>
@@ -3102,8 +3106,12 @@
         <v>184</v>
       </c>
       <c r="I6" s="5"/>
-      <c r="J6" s="7"/>
-      <c r="K6" s="5"/>
+      <c r="J6" s="7">
+        <v>46156</v>
+      </c>
+      <c r="K6" s="5" t="s">
+        <v>185</v>
+      </c>
       <c r="L6" s="5"/>
       <c r="M6" s="5"/>
       <c r="P6" s="40"/>
@@ -5700,18 +5708,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="88cc3c26-756f-41ab-80ed-43e7289fee5b">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="55239288-d498-4dd6-9609-491b39ec8fae" xsi:nil="true"/>
-    <MediaLengthInSeconds xmlns="88cc3c26-756f-41ab-80ed-43e7289fee5b" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x01010058BEBA3CD4E69545839402B5D4E5400B" ma:contentTypeVersion="13" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="85fadafb228503a8e253560e9cdffc69">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="88cc3c26-756f-41ab-80ed-43e7289fee5b" xmlns:ns3="55239288-d498-4dd6-9609-491b39ec8fae" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9785dde68d2e35ac7b66dd15e8e44124" ns2:_="" ns3:_="">
     <xsd:import namespace="88cc3c26-756f-41ab-80ed-43e7289fee5b"/>
@@ -5918,6 +5914,18 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="88cc3c26-756f-41ab-80ed-43e7289fee5b">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="55239288-d498-4dd6-9609-491b39ec8fae" xsi:nil="true"/>
+    <MediaLengthInSeconds xmlns="88cc3c26-756f-41ab-80ed-43e7289fee5b" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{24E212E4-ADE4-43F3-9F44-32B431C26D50}">
   <ds:schemaRefs>
@@ -5927,6 +5935,25 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9660893E-02E4-4B08-BC00-3F4A8BDDE437}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="88cc3c26-756f-41ab-80ed-43e7289fee5b"/>
+    <ds:schemaRef ds:uri="55239288-d498-4dd6-9609-491b39ec8fae"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC8775BF-FCD4-4761-95F0-599CE77DEFAA}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
@@ -5943,23 +5970,4 @@
     <ds:schemaRef ds:uri="55239288-d498-4dd6-9609-491b39ec8fae"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9660893E-02E4-4B08-BC00-3F4A8BDDE437}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="88cc3c26-756f-41ab-80ed-43e7289fee5b"/>
-    <ds:schemaRef ds:uri="55239288-d498-4dd6-9609-491b39ec8fae"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/ユースケース記述テスト仕様書.xlsx
+++ b/ユースケース記述テスト仕様書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\s_sakagami\git\gamityansoftware\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40F34AC9-C9D7-436B-B57D-DCDE5260B7AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADA1F51B-B894-4E5E-92E5-9F2EAFF3D0C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="1140" windowWidth="15130" windowHeight="8470" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="テスト仕様書" sheetId="5" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="187">
   <si>
     <t>ユースケース記述テスト仕様書</t>
     <rPh sb="6" eb="8">
@@ -2087,6 +2087,13 @@
     <t>坂上</t>
     <rPh sb="0" eb="2">
       <t>サカガミ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>齋藤</t>
+    <rPh sb="0" eb="2">
+      <t>サイトウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -3276,10 +3283,16 @@
       <c r="G12" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="H12" s="5"/>
+      <c r="H12" s="5" t="s">
+        <v>184</v>
+      </c>
       <c r="I12" s="5"/>
-      <c r="J12" s="7"/>
-      <c r="K12" s="5"/>
+      <c r="J12" s="7">
+        <v>46156</v>
+      </c>
+      <c r="K12" s="5" t="s">
+        <v>186</v>
+      </c>
       <c r="L12" s="5"/>
       <c r="M12" s="5"/>
     </row>
@@ -3296,10 +3309,16 @@
       <c r="G13" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="H13" s="5"/>
+      <c r="H13" s="5" t="s">
+        <v>184</v>
+      </c>
       <c r="I13" s="5"/>
-      <c r="J13" s="7"/>
-      <c r="K13" s="5"/>
+      <c r="J13" s="7">
+        <v>46156</v>
+      </c>
+      <c r="K13" s="5" t="s">
+        <v>186</v>
+      </c>
       <c r="L13" s="5"/>
       <c r="M13" s="5"/>
     </row>
@@ -3320,10 +3339,16 @@
       <c r="G14" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="H14" s="5"/>
+      <c r="H14" s="5" t="s">
+        <v>184</v>
+      </c>
       <c r="I14" s="5"/>
-      <c r="J14" s="7"/>
-      <c r="K14" s="5"/>
+      <c r="J14" s="7">
+        <v>46156</v>
+      </c>
+      <c r="K14" s="5" t="s">
+        <v>186</v>
+      </c>
       <c r="L14" s="5"/>
       <c r="M14" s="5"/>
     </row>
@@ -3348,10 +3373,16 @@
       <c r="G15" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="H15" s="5"/>
+      <c r="H15" s="5" t="s">
+        <v>184</v>
+      </c>
       <c r="I15" s="5"/>
-      <c r="J15" s="7"/>
-      <c r="K15" s="5"/>
+      <c r="J15" s="7">
+        <v>46156</v>
+      </c>
+      <c r="K15" s="5" t="s">
+        <v>186</v>
+      </c>
       <c r="L15" s="5"/>
       <c r="M15" s="5"/>
     </row>
@@ -3368,10 +3399,16 @@
       <c r="G16" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="H16" s="5"/>
+      <c r="H16" s="5" t="s">
+        <v>184</v>
+      </c>
       <c r="I16" s="5"/>
-      <c r="J16" s="7"/>
-      <c r="K16" s="5"/>
+      <c r="J16" s="7">
+        <v>46156</v>
+      </c>
+      <c r="K16" s="5" t="s">
+        <v>186</v>
+      </c>
       <c r="L16" s="5"/>
       <c r="M16" s="5"/>
     </row>
@@ -3392,10 +3429,16 @@
       <c r="G17" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="H17" s="5"/>
+      <c r="H17" s="5" t="s">
+        <v>184</v>
+      </c>
       <c r="I17" s="5"/>
-      <c r="J17" s="7"/>
-      <c r="K17" s="5"/>
+      <c r="J17" s="7">
+        <v>46156</v>
+      </c>
+      <c r="K17" s="5" t="s">
+        <v>186</v>
+      </c>
       <c r="L17" s="5"/>
       <c r="M17" s="5"/>
     </row>
@@ -3412,10 +3455,16 @@
       <c r="G18" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="H18" s="5"/>
+      <c r="H18" s="5" t="s">
+        <v>184</v>
+      </c>
       <c r="I18" s="5"/>
-      <c r="J18" s="7"/>
-      <c r="K18" s="5"/>
+      <c r="J18" s="7">
+        <v>46156</v>
+      </c>
+      <c r="K18" s="5" t="s">
+        <v>186</v>
+      </c>
       <c r="L18" s="5"/>
       <c r="M18" s="5"/>
     </row>
@@ -3436,10 +3485,16 @@
       <c r="G19" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="H19" s="5"/>
+      <c r="H19" s="5" t="s">
+        <v>184</v>
+      </c>
       <c r="I19" s="5"/>
-      <c r="J19" s="7"/>
-      <c r="K19" s="5"/>
+      <c r="J19" s="7">
+        <v>46156</v>
+      </c>
+      <c r="K19" s="5" t="s">
+        <v>186</v>
+      </c>
       <c r="L19" s="5"/>
       <c r="M19" s="5"/>
     </row>
@@ -3456,10 +3511,16 @@
       <c r="G20" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="H20" s="5"/>
+      <c r="H20" s="5" t="s">
+        <v>184</v>
+      </c>
       <c r="I20" s="5"/>
-      <c r="J20" s="7"/>
-      <c r="K20" s="5"/>
+      <c r="J20" s="7">
+        <v>46156</v>
+      </c>
+      <c r="K20" s="5" t="s">
+        <v>186</v>
+      </c>
       <c r="L20" s="5"/>
       <c r="M20" s="5"/>
     </row>
@@ -3476,10 +3537,16 @@
       <c r="G21" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="H21" s="5"/>
+      <c r="H21" s="5" t="s">
+        <v>184</v>
+      </c>
       <c r="I21" s="5"/>
-      <c r="J21" s="7"/>
-      <c r="K21" s="5"/>
+      <c r="J21" s="7">
+        <v>46156</v>
+      </c>
+      <c r="K21" s="5" t="s">
+        <v>186</v>
+      </c>
       <c r="L21" s="5"/>
       <c r="M21" s="5"/>
     </row>
@@ -3500,10 +3567,16 @@
       <c r="G22" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="H22" s="5"/>
+      <c r="H22" s="5" t="s">
+        <v>184</v>
+      </c>
       <c r="I22" s="5"/>
-      <c r="J22" s="7"/>
-      <c r="K22" s="5"/>
+      <c r="J22" s="7">
+        <v>46156</v>
+      </c>
+      <c r="K22" s="5" t="s">
+        <v>186</v>
+      </c>
       <c r="L22" s="5"/>
       <c r="M22" s="5"/>
     </row>
@@ -3520,10 +3593,16 @@
       <c r="G23" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="H23" s="5"/>
+      <c r="H23" s="5" t="s">
+        <v>184</v>
+      </c>
       <c r="I23" s="5"/>
-      <c r="J23" s="7"/>
-      <c r="K23" s="5"/>
+      <c r="J23" s="7">
+        <v>46156</v>
+      </c>
+      <c r="K23" s="5" t="s">
+        <v>186</v>
+      </c>
       <c r="L23" s="5"/>
       <c r="M23" s="5"/>
     </row>
@@ -5699,12 +5778,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="88cc3c26-756f-41ab-80ed-43e7289fee5b">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="55239288-d498-4dd6-9609-491b39ec8fae" xsi:nil="true"/>
+    <MediaLengthInSeconds xmlns="88cc3c26-756f-41ab-80ed-43e7289fee5b" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5915,21 +5997,29 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="88cc3c26-756f-41ab-80ed-43e7289fee5b">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="55239288-d498-4dd6-9609-491b39ec8fae" xsi:nil="true"/>
-    <MediaLengthInSeconds xmlns="88cc3c26-756f-41ab-80ed-43e7289fee5b" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{24E212E4-ADE4-43F3-9F44-32B431C26D50}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC8775BF-FCD4-4761-95F0-599CE77DEFAA}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="4707ffff-3746-4042-a13f-bfbbbbe730e0"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="96e9746f-acab-410f-8363-815e1ac6f97e"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="88cc3c26-756f-41ab-80ed-43e7289fee5b"/>
+    <ds:schemaRef ds:uri="55239288-d498-4dd6-9609-491b39ec8fae"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -5954,20 +6044,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC8775BF-FCD4-4761-95F0-599CE77DEFAA}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{24E212E4-ADE4-43F3-9F44-32B431C26D50}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="4707ffff-3746-4042-a13f-bfbbbbe730e0"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="96e9746f-acab-410f-8363-815e1ac6f97e"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="88cc3c26-756f-41ab-80ed-43e7289fee5b"/>
-    <ds:schemaRef ds:uri="55239288-d498-4dd6-9609-491b39ec8fae"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/ユースケース記述テスト仕様書.xlsx
+++ b/ユースケース記述テスト仕様書.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\s_sakagami\git\gamityansoftware\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\class_project\gamityansoftware\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADA1F51B-B894-4E5E-92E5-9F2EAFF3D0C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A870776-6C00-43A8-95E0-1097BD08CE5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="192">
   <si>
     <t>ユースケース記述テスト仕様書</t>
     <rPh sb="6" eb="8">
@@ -2094,6 +2094,61 @@
     <t>齋藤</t>
     <rPh sb="0" eb="2">
       <t>サイトウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>期待値通り</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>田上</t>
+    <rPh sb="0" eb="2">
+      <t>タノウエ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>期待値通り
+入力された項目は値を保持</t>
+    <rPh sb="6" eb="8">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>コウモク</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>アタイ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ホジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>期待値通り</t>
+    <rPh sb="0" eb="3">
+      <t>キタイチ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ドオ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>期待値通り
+入力値は保持されない</t>
+    <rPh sb="0" eb="3">
+      <t>キタイチ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ドオ</t>
+    </rPh>
+    <rPh sb="6" eb="9">
+      <t>ニュウリョクチ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ホジ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -4587,10 +4642,16 @@
       <c r="G65" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="H65" s="5"/>
+      <c r="H65" s="5" t="s">
+        <v>187</v>
+      </c>
       <c r="I65" s="5"/>
-      <c r="J65" s="7"/>
-      <c r="K65" s="5"/>
+      <c r="J65" s="7">
+        <v>46157</v>
+      </c>
+      <c r="K65" s="5" t="s">
+        <v>188</v>
+      </c>
       <c r="L65" s="5"/>
       <c r="M65" s="5"/>
     </row>
@@ -4615,10 +4676,16 @@
       <c r="G66" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="H66" s="5"/>
+      <c r="H66" s="6" t="s">
+        <v>189</v>
+      </c>
       <c r="I66" s="5"/>
-      <c r="J66" s="7"/>
-      <c r="K66" s="5"/>
+      <c r="J66" s="7">
+        <v>46157</v>
+      </c>
+      <c r="K66" s="5" t="s">
+        <v>188</v>
+      </c>
       <c r="L66" s="5"/>
       <c r="M66" s="5"/>
     </row>
@@ -4635,10 +4702,16 @@
       <c r="G67" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="H67" s="5"/>
+      <c r="H67" s="5" t="s">
+        <v>187</v>
+      </c>
       <c r="I67" s="5"/>
-      <c r="J67" s="7"/>
-      <c r="K67" s="5"/>
+      <c r="J67" s="7">
+        <v>46157</v>
+      </c>
+      <c r="K67" s="5" t="s">
+        <v>188</v>
+      </c>
       <c r="L67" s="5"/>
       <c r="M67" s="5"/>
     </row>
@@ -4661,10 +4734,16 @@
       <c r="G68" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="H68" s="5"/>
+      <c r="H68" s="5" t="s">
+        <v>190</v>
+      </c>
       <c r="I68" s="5"/>
-      <c r="J68" s="7"/>
-      <c r="K68" s="5"/>
+      <c r="J68" s="7">
+        <v>46157</v>
+      </c>
+      <c r="K68" s="5" t="s">
+        <v>188</v>
+      </c>
       <c r="L68" s="5"/>
       <c r="M68" s="5"/>
     </row>
@@ -4689,10 +4768,16 @@
       <c r="G69" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="H69" s="5"/>
+      <c r="H69" s="6" t="s">
+        <v>191</v>
+      </c>
       <c r="I69" s="5"/>
-      <c r="J69" s="7"/>
-      <c r="K69" s="5"/>
+      <c r="J69" s="7">
+        <v>46157</v>
+      </c>
+      <c r="K69" s="5" t="s">
+        <v>188</v>
+      </c>
       <c r="L69" s="5"/>
       <c r="M69" s="5"/>
     </row>
@@ -4709,10 +4794,16 @@
       <c r="G70" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="H70" s="5"/>
+      <c r="H70" s="5" t="s">
+        <v>190</v>
+      </c>
       <c r="I70" s="5"/>
-      <c r="J70" s="7"/>
-      <c r="K70" s="5"/>
+      <c r="J70" s="7">
+        <v>46157</v>
+      </c>
+      <c r="K70" s="5" t="s">
+        <v>188</v>
+      </c>
       <c r="L70" s="5"/>
       <c r="M70" s="5"/>
     </row>
@@ -4733,10 +4824,16 @@
       <c r="G71" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="H71" s="5"/>
+      <c r="H71" s="5" t="s">
+        <v>190</v>
+      </c>
       <c r="I71" s="5"/>
-      <c r="J71" s="7"/>
-      <c r="K71" s="5"/>
+      <c r="J71" s="7">
+        <v>46157</v>
+      </c>
+      <c r="K71" s="5" t="s">
+        <v>188</v>
+      </c>
       <c r="L71" s="5"/>
       <c r="M71" s="5"/>
     </row>
@@ -4753,10 +4850,16 @@
       <c r="G72" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="H72" s="5"/>
+      <c r="H72" s="5" t="s">
+        <v>190</v>
+      </c>
       <c r="I72" s="5"/>
-      <c r="J72" s="7"/>
-      <c r="K72" s="5"/>
+      <c r="J72" s="7">
+        <v>46157</v>
+      </c>
+      <c r="K72" s="5" t="s">
+        <v>188</v>
+      </c>
       <c r="L72" s="5"/>
       <c r="M72" s="5"/>
     </row>
@@ -4777,10 +4880,16 @@
       <c r="G73" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="H73" s="5"/>
+      <c r="H73" s="5" t="s">
+        <v>190</v>
+      </c>
       <c r="I73" s="5"/>
-      <c r="J73" s="7"/>
-      <c r="K73" s="5"/>
+      <c r="J73" s="7">
+        <v>46157</v>
+      </c>
+      <c r="K73" s="5" t="s">
+        <v>188</v>
+      </c>
       <c r="L73" s="5"/>
       <c r="M73" s="5"/>
     </row>
@@ -4805,10 +4914,16 @@
       <c r="G74" s="6" t="s">
         <v>164</v>
       </c>
-      <c r="H74" s="5"/>
+      <c r="H74" s="6" t="s">
+        <v>189</v>
+      </c>
       <c r="I74" s="5"/>
-      <c r="J74" s="7"/>
-      <c r="K74" s="5"/>
+      <c r="J74" s="7">
+        <v>46157</v>
+      </c>
+      <c r="K74" s="5" t="s">
+        <v>188</v>
+      </c>
       <c r="L74" s="5"/>
       <c r="M74" s="5"/>
     </row>
@@ -4825,10 +4940,16 @@
       <c r="G75" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="H75" s="5"/>
+      <c r="H75" s="5" t="s">
+        <v>190</v>
+      </c>
       <c r="I75" s="5"/>
-      <c r="J75" s="7"/>
-      <c r="K75" s="5"/>
+      <c r="J75" s="7">
+        <v>46157</v>
+      </c>
+      <c r="K75" s="5" t="s">
+        <v>188</v>
+      </c>
       <c r="L75" s="5"/>
       <c r="M75" s="5"/>
     </row>
@@ -4851,10 +4972,16 @@
       <c r="G76" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="H76" s="5"/>
+      <c r="H76" s="5" t="s">
+        <v>190</v>
+      </c>
       <c r="I76" s="5"/>
-      <c r="J76" s="7"/>
-      <c r="K76" s="5"/>
+      <c r="J76" s="7">
+        <v>46157</v>
+      </c>
+      <c r="K76" s="5" t="s">
+        <v>188</v>
+      </c>
       <c r="L76" s="5"/>
       <c r="M76" s="5"/>
     </row>
@@ -4871,10 +4998,16 @@
       <c r="G77" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="H77" s="5"/>
+      <c r="H77" s="5" t="s">
+        <v>190</v>
+      </c>
       <c r="I77" s="5"/>
-      <c r="J77" s="7"/>
-      <c r="K77" s="5"/>
+      <c r="J77" s="7">
+        <v>46157</v>
+      </c>
+      <c r="K77" s="5" t="s">
+        <v>188</v>
+      </c>
       <c r="L77" s="5"/>
       <c r="M77" s="5"/>
     </row>
@@ -4895,10 +5028,16 @@
       <c r="G78" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="H78" s="5"/>
+      <c r="H78" s="5" t="s">
+        <v>190</v>
+      </c>
       <c r="I78" s="5"/>
-      <c r="J78" s="7"/>
-      <c r="K78" s="5"/>
+      <c r="J78" s="7">
+        <v>46157</v>
+      </c>
+      <c r="K78" s="5" t="s">
+        <v>188</v>
+      </c>
       <c r="L78" s="5"/>
       <c r="M78" s="5"/>
     </row>
@@ -4915,10 +5054,16 @@
       <c r="G79" s="6" t="s">
         <v>171</v>
       </c>
-      <c r="H79" s="5"/>
+      <c r="H79" s="5" t="s">
+        <v>190</v>
+      </c>
       <c r="I79" s="5"/>
-      <c r="J79" s="7"/>
-      <c r="K79" s="5"/>
+      <c r="J79" s="7">
+        <v>46157</v>
+      </c>
+      <c r="K79" s="5" t="s">
+        <v>188</v>
+      </c>
       <c r="L79" s="5"/>
       <c r="M79" s="5"/>
     </row>
@@ -4939,10 +5084,16 @@
       <c r="G80" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="H80" s="5"/>
+      <c r="H80" s="5" t="s">
+        <v>190</v>
+      </c>
       <c r="I80" s="5"/>
-      <c r="J80" s="7"/>
-      <c r="K80" s="5"/>
+      <c r="J80" s="7">
+        <v>46157</v>
+      </c>
+      <c r="K80" s="5" t="s">
+        <v>188</v>
+      </c>
       <c r="L80" s="5"/>
       <c r="M80" s="5"/>
     </row>
@@ -4967,10 +5118,16 @@
       <c r="G81" s="6" t="s">
         <v>164</v>
       </c>
-      <c r="H81" s="5"/>
+      <c r="H81" s="5" t="s">
+        <v>190</v>
+      </c>
       <c r="I81" s="5"/>
-      <c r="J81" s="7"/>
-      <c r="K81" s="5"/>
+      <c r="J81" s="7">
+        <v>46157</v>
+      </c>
+      <c r="K81" s="5" t="s">
+        <v>188</v>
+      </c>
       <c r="L81" s="5"/>
       <c r="M81" s="5"/>
     </row>
@@ -4987,10 +5144,16 @@
       <c r="G82" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="H82" s="5"/>
+      <c r="H82" s="5" t="s">
+        <v>190</v>
+      </c>
       <c r="I82" s="5"/>
-      <c r="J82" s="7"/>
-      <c r="K82" s="5"/>
+      <c r="J82" s="7">
+        <v>46157</v>
+      </c>
+      <c r="K82" s="5" t="s">
+        <v>188</v>
+      </c>
       <c r="L82" s="5"/>
       <c r="M82" s="5"/>
     </row>
@@ -5013,10 +5176,16 @@
       <c r="G83" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="H83" s="5"/>
+      <c r="H83" s="5" t="s">
+        <v>190</v>
+      </c>
       <c r="I83" s="5"/>
-      <c r="J83" s="7"/>
-      <c r="K83" s="5"/>
+      <c r="J83" s="7">
+        <v>46157</v>
+      </c>
+      <c r="K83" s="5" t="s">
+        <v>188</v>
+      </c>
       <c r="L83" s="5"/>
       <c r="M83" s="5"/>
     </row>
@@ -5033,10 +5202,16 @@
       <c r="G84" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="H84" s="5"/>
+      <c r="H84" s="5" t="s">
+        <v>190</v>
+      </c>
       <c r="I84" s="5"/>
-      <c r="J84" s="7"/>
-      <c r="K84" s="5"/>
+      <c r="J84" s="7">
+        <v>46157</v>
+      </c>
+      <c r="K84" s="5" t="s">
+        <v>188</v>
+      </c>
       <c r="L84" s="5"/>
       <c r="M84" s="5"/>
     </row>
@@ -5057,10 +5232,16 @@
       <c r="G85" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="H85" s="5"/>
+      <c r="H85" s="5" t="s">
+        <v>190</v>
+      </c>
       <c r="I85" s="5"/>
-      <c r="J85" s="7"/>
-      <c r="K85" s="5"/>
+      <c r="J85" s="7">
+        <v>46157</v>
+      </c>
+      <c r="K85" s="5" t="s">
+        <v>188</v>
+      </c>
       <c r="L85" s="5"/>
       <c r="M85" s="5"/>
     </row>
@@ -5077,10 +5258,16 @@
       <c r="G86" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="H86" s="5"/>
+      <c r="H86" s="5" t="s">
+        <v>190</v>
+      </c>
       <c r="I86" s="5"/>
-      <c r="J86" s="7"/>
-      <c r="K86" s="5"/>
+      <c r="J86" s="7">
+        <v>46157</v>
+      </c>
+      <c r="K86" s="5" t="s">
+        <v>188</v>
+      </c>
       <c r="L86" s="5"/>
       <c r="M86" s="5"/>
     </row>
@@ -5778,15 +5965,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="88cc3c26-756f-41ab-80ed-43e7289fee5b">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="55239288-d498-4dd6-9609-491b39ec8fae" xsi:nil="true"/>
-    <MediaLengthInSeconds xmlns="88cc3c26-756f-41ab-80ed-43e7289fee5b" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5997,29 +6181,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="88cc3c26-756f-41ab-80ed-43e7289fee5b">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="55239288-d498-4dd6-9609-491b39ec8fae" xsi:nil="true"/>
+    <MediaLengthInSeconds xmlns="88cc3c26-756f-41ab-80ed-43e7289fee5b" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC8775BF-FCD4-4761-95F0-599CE77DEFAA}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{24E212E4-ADE4-43F3-9F44-32B431C26D50}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="4707ffff-3746-4042-a13f-bfbbbbe730e0"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="96e9746f-acab-410f-8363-815e1ac6f97e"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="88cc3c26-756f-41ab-80ed-43e7289fee5b"/>
-    <ds:schemaRef ds:uri="55239288-d498-4dd6-9609-491b39ec8fae"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -6044,9 +6220,20 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{24E212E4-ADE4-43F3-9F44-32B431C26D50}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC8775BF-FCD4-4761-95F0-599CE77DEFAA}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="4707ffff-3746-4042-a13f-bfbbbbe730e0"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="96e9746f-acab-410f-8363-815e1ac6f97e"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="88cc3c26-756f-41ab-80ed-43e7289fee5b"/>
+    <ds:schemaRef ds:uri="55239288-d498-4dd6-9609-491b39ec8fae"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>